--- a/Deliverables/BOM/Electrode-Board/eSpark BOM-Elec-Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/eSpark BOM-Elec-Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5EB104-6FB5-48BA-939A-05A0703998B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CB4E3D-CC6A-4D71-B5F2-46B4D656015B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1078,6 +1078,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1109,9 +1112,6 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1489,15 +1489,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1547,7 +1547,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="68"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1572,7 +1572,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="69"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1597,7 +1597,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="69"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1618,7 +1618,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="69"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1639,7 +1639,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="69"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1660,7 +1660,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="69"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2568,7 +2568,7 @@
       <c r="F25" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="75" t="s">
+      <c r="G25" s="65" t="s">
         <v>73</v>
       </c>
       <c r="H25" s="37" t="s">
@@ -2620,17 +2620,17 @@
       <c r="K26" s="45"/>
       <c r="L26" s="45"/>
       <c r="M26" s="45"/>
-      <c r="N26" s="73" t="s">
+      <c r="N26" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
       <c r="Q26" s="48">
         <f>SUM(Q10:Q25)</f>
         <v>43.323599999999999</v>
       </c>
-      <c r="R26" s="69"/>
-      <c r="S26" s="70"/>
+      <c r="R26" s="70"/>
+      <c r="S26" s="71"/>
     </row>
     <row r="27" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -2646,17 +2646,17 @@
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
-      <c r="N27" s="73" t="s">
+      <c r="N27" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="O27" s="74"/>
-      <c r="P27" s="74"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
       <c r="Q27" s="49">
         <f>Q26/5</f>
         <v>8.6647199999999991</v>
       </c>
-      <c r="R27" s="71"/>
-      <c r="S27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
